--- a/data/csv/SP500.xlsx
+++ b/data/csv/SP500.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfpin\Desktop\Projects\gravity\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5289CA1E-CEC4-4087-8B09-2A4A4B82FC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38FE8A1-57E1-498A-B677-CCF8283B386F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5CBD7DF0-9BE8-4B06-9E4B-6321E64942CB}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="513">
   <si>
     <t>Ticker</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>BF.B</t>
-  </si>
-  <si>
     <t>BG</t>
   </si>
   <si>
@@ -475,9 +472,6 @@
     <t>BLK</t>
   </si>
   <si>
-    <t>BRK.B</t>
-  </si>
-  <si>
     <t>BRO</t>
   </si>
   <si>
@@ -737,9 +731,6 @@
   </si>
   <si>
     <t>HCA</t>
-  </si>
-  <si>
-    <t>HOLX</t>
   </si>
   <si>
     <t>HSIC</t>
@@ -2428,7 +2419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF72847-80E3-4E00-933E-448160A236EF}">
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B501"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -3292,15 +3283,15 @@
         <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109" t="s">
         <v>112</v>
-      </c>
-      <c r="B109" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -3308,7 +3299,7 @@
         <v>114</v>
       </c>
       <c r="B110" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -3316,7 +3307,7 @@
         <v>115</v>
       </c>
       <c r="B111" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -3324,7 +3315,7 @@
         <v>116</v>
       </c>
       <c r="B112" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
@@ -3332,7 +3323,7 @@
         <v>117</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
@@ -3340,7 +3331,7 @@
         <v>118</v>
       </c>
       <c r="B114" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
@@ -3348,7 +3339,7 @@
         <v>119</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
@@ -3356,7 +3347,7 @@
         <v>120</v>
       </c>
       <c r="B116" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
@@ -3364,7 +3355,7 @@
         <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
@@ -3372,7 +3363,7 @@
         <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -3380,7 +3371,7 @@
         <v>123</v>
       </c>
       <c r="B119" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -3388,7 +3379,7 @@
         <v>124</v>
       </c>
       <c r="B120" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -3396,7 +3387,7 @@
         <v>125</v>
       </c>
       <c r="B121" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -3404,7 +3395,7 @@
         <v>126</v>
       </c>
       <c r="B122" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -3412,7 +3403,7 @@
         <v>127</v>
       </c>
       <c r="B123" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -3420,7 +3411,7 @@
         <v>128</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -3428,7 +3419,7 @@
         <v>129</v>
       </c>
       <c r="B125" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -3436,7 +3427,7 @@
         <v>130</v>
       </c>
       <c r="B126" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -3444,7 +3435,7 @@
         <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -3452,7 +3443,7 @@
         <v>132</v>
       </c>
       <c r="B128" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -3460,7 +3451,7 @@
         <v>133</v>
       </c>
       <c r="B129" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -3468,15 +3459,15 @@
         <v>134</v>
       </c>
       <c r="B130" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -3484,7 +3475,7 @@
         <v>137</v>
       </c>
       <c r="B132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
@@ -3492,7 +3483,7 @@
         <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -3500,7 +3491,7 @@
         <v>139</v>
       </c>
       <c r="B134" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -3508,7 +3499,7 @@
         <v>140</v>
       </c>
       <c r="B135" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -3516,7 +3507,7 @@
         <v>141</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
@@ -3524,7 +3515,7 @@
         <v>142</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
@@ -3532,7 +3523,7 @@
         <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -3540,7 +3531,7 @@
         <v>144</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -3548,7 +3539,7 @@
         <v>145</v>
       </c>
       <c r="B140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -3556,7 +3547,7 @@
         <v>146</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
@@ -3564,7 +3555,7 @@
         <v>147</v>
       </c>
       <c r="B142" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
@@ -3572,7 +3563,7 @@
         <v>148</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -3580,7 +3571,7 @@
         <v>149</v>
       </c>
       <c r="B144" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
@@ -3588,7 +3579,7 @@
         <v>150</v>
       </c>
       <c r="B145" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
@@ -3596,7 +3587,7 @@
         <v>151</v>
       </c>
       <c r="B146" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
@@ -3604,7 +3595,7 @@
         <v>152</v>
       </c>
       <c r="B147" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -3612,7 +3603,7 @@
         <v>153</v>
       </c>
       <c r="B148" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -3620,7 +3611,7 @@
         <v>154</v>
       </c>
       <c r="B149" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -3628,7 +3619,7 @@
         <v>155</v>
       </c>
       <c r="B150" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -3636,7 +3627,7 @@
         <v>156</v>
       </c>
       <c r="B151" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -3644,7 +3635,7 @@
         <v>157</v>
       </c>
       <c r="B152" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -3652,7 +3643,7 @@
         <v>158</v>
       </c>
       <c r="B153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -3660,7 +3651,7 @@
         <v>159</v>
       </c>
       <c r="B154" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -3668,7 +3659,7 @@
         <v>160</v>
       </c>
       <c r="B155" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -3676,7 +3667,7 @@
         <v>161</v>
       </c>
       <c r="B156" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -3684,7 +3675,7 @@
         <v>162</v>
       </c>
       <c r="B157" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -3692,7 +3683,7 @@
         <v>163</v>
       </c>
       <c r="B158" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -3700,7 +3691,7 @@
         <v>164</v>
       </c>
       <c r="B159" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -3708,7 +3699,7 @@
         <v>165</v>
       </c>
       <c r="B160" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -3716,7 +3707,7 @@
         <v>166</v>
       </c>
       <c r="B161" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -3724,7 +3715,7 @@
         <v>167</v>
       </c>
       <c r="B162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -3732,7 +3723,7 @@
         <v>168</v>
       </c>
       <c r="B163" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -3740,7 +3731,7 @@
         <v>169</v>
       </c>
       <c r="B164" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -3748,7 +3739,7 @@
         <v>170</v>
       </c>
       <c r="B165" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -3756,7 +3747,7 @@
         <v>171</v>
       </c>
       <c r="B166" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -3764,7 +3755,7 @@
         <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -3772,7 +3763,7 @@
         <v>173</v>
       </c>
       <c r="B168" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -3780,7 +3771,7 @@
         <v>174</v>
       </c>
       <c r="B169" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -3788,7 +3779,7 @@
         <v>175</v>
       </c>
       <c r="B170" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
@@ -3796,7 +3787,7 @@
         <v>176</v>
       </c>
       <c r="B171" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
@@ -3804,7 +3795,7 @@
         <v>177</v>
       </c>
       <c r="B172" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
@@ -3812,7 +3803,7 @@
         <v>178</v>
       </c>
       <c r="B173" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -3820,7 +3811,7 @@
         <v>179</v>
       </c>
       <c r="B174" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -3828,7 +3819,7 @@
         <v>180</v>
       </c>
       <c r="B175" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -3836,7 +3827,7 @@
         <v>181</v>
       </c>
       <c r="B176" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -3844,7 +3835,7 @@
         <v>182</v>
       </c>
       <c r="B177" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -3852,7 +3843,7 @@
         <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -3860,7 +3851,7 @@
         <v>184</v>
       </c>
       <c r="B179" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -3868,7 +3859,7 @@
         <v>185</v>
       </c>
       <c r="B180" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -3876,7 +3867,7 @@
         <v>186</v>
       </c>
       <c r="B181" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -3884,7 +3875,7 @@
         <v>187</v>
       </c>
       <c r="B182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -3892,7 +3883,7 @@
         <v>188</v>
       </c>
       <c r="B183" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -3900,7 +3891,7 @@
         <v>189</v>
       </c>
       <c r="B184" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -3908,7 +3899,7 @@
         <v>190</v>
       </c>
       <c r="B185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -3916,7 +3907,7 @@
         <v>191</v>
       </c>
       <c r="B186" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -3924,7 +3915,7 @@
         <v>192</v>
       </c>
       <c r="B187" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -3932,7 +3923,7 @@
         <v>193</v>
       </c>
       <c r="B188" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -3940,7 +3931,7 @@
         <v>194</v>
       </c>
       <c r="B189" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -3948,7 +3939,7 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -3956,7 +3947,7 @@
         <v>196</v>
       </c>
       <c r="B191" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -3964,7 +3955,7 @@
         <v>197</v>
       </c>
       <c r="B192" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -3972,7 +3963,7 @@
         <v>198</v>
       </c>
       <c r="B193" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -3980,7 +3971,7 @@
         <v>199</v>
       </c>
       <c r="B194" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -3988,7 +3979,7 @@
         <v>200</v>
       </c>
       <c r="B195" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -3996,7 +3987,7 @@
         <v>201</v>
       </c>
       <c r="B196" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -4004,7 +3995,7 @@
         <v>202</v>
       </c>
       <c r="B197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -4012,7 +4003,7 @@
         <v>203</v>
       </c>
       <c r="B198" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -4020,7 +4011,7 @@
         <v>204</v>
       </c>
       <c r="B199" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -4028,7 +4019,7 @@
         <v>205</v>
       </c>
       <c r="B200" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -4036,7 +4027,7 @@
         <v>206</v>
       </c>
       <c r="B201" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -4044,7 +4035,7 @@
         <v>207</v>
       </c>
       <c r="B202" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -4052,7 +4043,7 @@
         <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -4060,7 +4051,7 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -4068,23 +4059,23 @@
         <v>210</v>
       </c>
       <c r="B205" t="s">
-        <v>136</v>
+        <v>211</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
+        <v>212</v>
+      </c>
+      <c r="B206" t="s">
         <v>211</v>
-      </c>
-      <c r="B206" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B207" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -4092,7 +4083,7 @@
         <v>214</v>
       </c>
       <c r="B208" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -4100,7 +4091,7 @@
         <v>215</v>
       </c>
       <c r="B209" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -4108,7 +4099,7 @@
         <v>216</v>
       </c>
       <c r="B210" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -4116,7 +4107,7 @@
         <v>217</v>
       </c>
       <c r="B211" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -4124,7 +4115,7 @@
         <v>218</v>
       </c>
       <c r="B212" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -4132,7 +4123,7 @@
         <v>219</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -4140,7 +4131,7 @@
         <v>220</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -4148,7 +4139,7 @@
         <v>221</v>
       </c>
       <c r="B215" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -4156,7 +4147,7 @@
         <v>222</v>
       </c>
       <c r="B216" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -4164,7 +4155,7 @@
         <v>223</v>
       </c>
       <c r="B217" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -4172,7 +4163,7 @@
         <v>224</v>
       </c>
       <c r="B218" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -4180,7 +4171,7 @@
         <v>225</v>
       </c>
       <c r="B219" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -4188,7 +4179,7 @@
         <v>226</v>
       </c>
       <c r="B220" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -4196,7 +4187,7 @@
         <v>227</v>
       </c>
       <c r="B221" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -4204,7 +4195,7 @@
         <v>228</v>
       </c>
       <c r="B222" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -4212,7 +4203,7 @@
         <v>229</v>
       </c>
       <c r="B223" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -4220,7 +4211,7 @@
         <v>230</v>
       </c>
       <c r="B224" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -4228,7 +4219,7 @@
         <v>231</v>
       </c>
       <c r="B225" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -4236,7 +4227,7 @@
         <v>232</v>
       </c>
       <c r="B226" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -4244,7 +4235,7 @@
         <v>233</v>
       </c>
       <c r="B227" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -4252,7 +4243,7 @@
         <v>234</v>
       </c>
       <c r="B228" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -4260,7 +4251,7 @@
         <v>235</v>
       </c>
       <c r="B229" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -4268,7 +4259,7 @@
         <v>236</v>
       </c>
       <c r="B230" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -4276,7 +4267,7 @@
         <v>237</v>
       </c>
       <c r="B231" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -4284,7 +4275,7 @@
         <v>238</v>
       </c>
       <c r="B232" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -4292,7 +4283,7 @@
         <v>239</v>
       </c>
       <c r="B233" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -4300,7 +4291,7 @@
         <v>240</v>
       </c>
       <c r="B234" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -4308,7 +4299,7 @@
         <v>241</v>
       </c>
       <c r="B235" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -4316,7 +4307,7 @@
         <v>242</v>
       </c>
       <c r="B236" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -4324,7 +4315,7 @@
         <v>243</v>
       </c>
       <c r="B237" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -4332,7 +4323,7 @@
         <v>244</v>
       </c>
       <c r="B238" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -4340,7 +4331,7 @@
         <v>245</v>
       </c>
       <c r="B239" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -4348,7 +4339,7 @@
         <v>246</v>
       </c>
       <c r="B240" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -4356,7 +4347,7 @@
         <v>247</v>
       </c>
       <c r="B241" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -4364,7 +4355,7 @@
         <v>248</v>
       </c>
       <c r="B242" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -4372,7 +4363,7 @@
         <v>249</v>
       </c>
       <c r="B243" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -4380,7 +4371,7 @@
         <v>250</v>
       </c>
       <c r="B244" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -4388,7 +4379,7 @@
         <v>251</v>
       </c>
       <c r="B245" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -4396,7 +4387,7 @@
         <v>252</v>
       </c>
       <c r="B246" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -4404,7 +4395,7 @@
         <v>253</v>
       </c>
       <c r="B247" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -4412,7 +4403,7 @@
         <v>254</v>
       </c>
       <c r="B248" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -4420,7 +4411,7 @@
         <v>255</v>
       </c>
       <c r="B249" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -4428,7 +4419,7 @@
         <v>256</v>
       </c>
       <c r="B250" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -4436,7 +4427,7 @@
         <v>257</v>
       </c>
       <c r="B251" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -4444,7 +4435,7 @@
         <v>258</v>
       </c>
       <c r="B252" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -4452,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="B253" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -4460,7 +4451,7 @@
         <v>260</v>
       </c>
       <c r="B254" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -4468,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="B255" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -4476,7 +4467,7 @@
         <v>262</v>
       </c>
       <c r="B256" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -4484,7 +4475,7 @@
         <v>263</v>
       </c>
       <c r="B257" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -4492,7 +4483,7 @@
         <v>264</v>
       </c>
       <c r="B258" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -4500,7 +4491,7 @@
         <v>265</v>
       </c>
       <c r="B259" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -4508,7 +4499,7 @@
         <v>266</v>
       </c>
       <c r="B260" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -4516,7 +4507,7 @@
         <v>267</v>
       </c>
       <c r="B261" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -4524,7 +4515,7 @@
         <v>268</v>
       </c>
       <c r="B262" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -4532,7 +4523,7 @@
         <v>269</v>
       </c>
       <c r="B263" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -4540,31 +4531,31 @@
         <v>270</v>
       </c>
       <c r="B264" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B265" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B266" t="s">
-        <v>213</v>
+        <v>271</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B267" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -4572,7 +4563,7 @@
         <v>275</v>
       </c>
       <c r="B268" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -4580,7 +4571,7 @@
         <v>276</v>
       </c>
       <c r="B269" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -4588,7 +4579,7 @@
         <v>277</v>
       </c>
       <c r="B270" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -4596,7 +4587,7 @@
         <v>278</v>
       </c>
       <c r="B271" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -4604,7 +4595,7 @@
         <v>279</v>
       </c>
       <c r="B272" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -4612,7 +4603,7 @@
         <v>280</v>
       </c>
       <c r="B273" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -4620,7 +4611,7 @@
         <v>281</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -4628,7 +4619,7 @@
         <v>282</v>
       </c>
       <c r="B275" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -4636,7 +4627,7 @@
         <v>283</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -4644,7 +4635,7 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -4652,7 +4643,7 @@
         <v>285</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -4660,7 +4651,7 @@
         <v>286</v>
       </c>
       <c r="B279" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -4668,7 +4659,7 @@
         <v>287</v>
       </c>
       <c r="B280" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -4676,7 +4667,7 @@
         <v>288</v>
       </c>
       <c r="B281" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -4684,7 +4675,7 @@
         <v>289</v>
       </c>
       <c r="B282" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -4692,7 +4683,7 @@
         <v>290</v>
       </c>
       <c r="B283" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -4700,7 +4691,7 @@
         <v>291</v>
       </c>
       <c r="B284" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -4708,7 +4699,7 @@
         <v>292</v>
       </c>
       <c r="B285" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -4716,7 +4707,7 @@
         <v>293</v>
       </c>
       <c r="B286" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -4724,7 +4715,7 @@
         <v>294</v>
       </c>
       <c r="B287" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -4732,7 +4723,7 @@
         <v>295</v>
       </c>
       <c r="B288" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -4740,7 +4731,7 @@
         <v>296</v>
       </c>
       <c r="B289" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -4748,7 +4739,7 @@
         <v>297</v>
       </c>
       <c r="B290" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -4756,7 +4747,7 @@
         <v>298</v>
       </c>
       <c r="B291" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -4764,7 +4755,7 @@
         <v>299</v>
       </c>
       <c r="B292" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -4772,7 +4763,7 @@
         <v>300</v>
       </c>
       <c r="B293" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -4780,7 +4771,7 @@
         <v>301</v>
       </c>
       <c r="B294" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -4788,7 +4779,7 @@
         <v>302</v>
       </c>
       <c r="B295" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -4796,7 +4787,7 @@
         <v>303</v>
       </c>
       <c r="B296" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -4804,7 +4795,7 @@
         <v>304</v>
       </c>
       <c r="B297" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -4812,7 +4803,7 @@
         <v>305</v>
       </c>
       <c r="B298" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -4820,7 +4811,7 @@
         <v>306</v>
       </c>
       <c r="B299" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -4828,7 +4819,7 @@
         <v>307</v>
       </c>
       <c r="B300" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -4836,7 +4827,7 @@
         <v>308</v>
       </c>
       <c r="B301" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -4844,7 +4835,7 @@
         <v>309</v>
       </c>
       <c r="B302" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -4852,7 +4843,7 @@
         <v>310</v>
       </c>
       <c r="B303" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -4860,7 +4851,7 @@
         <v>311</v>
       </c>
       <c r="B304" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -4868,7 +4859,7 @@
         <v>312</v>
       </c>
       <c r="B305" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -4876,7 +4867,7 @@
         <v>313</v>
       </c>
       <c r="B306" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -4884,7 +4875,7 @@
         <v>314</v>
       </c>
       <c r="B307" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -4892,7 +4883,7 @@
         <v>315</v>
       </c>
       <c r="B308" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -4900,7 +4891,7 @@
         <v>316</v>
       </c>
       <c r="B309" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -4908,7 +4899,7 @@
         <v>317</v>
       </c>
       <c r="B310" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -4916,7 +4907,7 @@
         <v>318</v>
       </c>
       <c r="B311" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -4924,7 +4915,7 @@
         <v>319</v>
       </c>
       <c r="B312" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -4932,7 +4923,7 @@
         <v>320</v>
       </c>
       <c r="B313" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -4940,7 +4931,7 @@
         <v>321</v>
       </c>
       <c r="B314" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -4948,7 +4939,7 @@
         <v>322</v>
       </c>
       <c r="B315" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -4956,7 +4947,7 @@
         <v>323</v>
       </c>
       <c r="B316" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
@@ -4964,7 +4955,7 @@
         <v>324</v>
       </c>
       <c r="B317" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -4972,7 +4963,7 @@
         <v>325</v>
       </c>
       <c r="B318" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -4980,7 +4971,7 @@
         <v>326</v>
       </c>
       <c r="B319" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -4988,7 +4979,7 @@
         <v>327</v>
       </c>
       <c r="B320" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -4996,7 +4987,7 @@
         <v>328</v>
       </c>
       <c r="B321" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -5004,7 +4995,7 @@
         <v>329</v>
       </c>
       <c r="B322" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -5012,7 +5003,7 @@
         <v>330</v>
       </c>
       <c r="B323" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -5020,7 +5011,7 @@
         <v>331</v>
       </c>
       <c r="B324" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -5028,7 +5019,7 @@
         <v>332</v>
       </c>
       <c r="B325" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -5036,7 +5027,7 @@
         <v>333</v>
       </c>
       <c r="B326" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -5044,7 +5035,7 @@
         <v>334</v>
       </c>
       <c r="B327" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -5052,7 +5043,7 @@
         <v>335</v>
       </c>
       <c r="B328" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -5060,7 +5051,7 @@
         <v>336</v>
       </c>
       <c r="B329" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -5068,7 +5059,7 @@
         <v>337</v>
       </c>
       <c r="B330" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -5076,7 +5067,7 @@
         <v>338</v>
       </c>
       <c r="B331" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -5084,7 +5075,7 @@
         <v>339</v>
       </c>
       <c r="B332" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -5092,7 +5083,7 @@
         <v>340</v>
       </c>
       <c r="B333" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -5100,7 +5091,7 @@
         <v>341</v>
       </c>
       <c r="B334" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -5108,7 +5099,7 @@
         <v>342</v>
       </c>
       <c r="B335" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -5116,7 +5107,7 @@
         <v>343</v>
       </c>
       <c r="B336" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -5124,7 +5115,7 @@
         <v>344</v>
       </c>
       <c r="B337" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -5132,7 +5123,7 @@
         <v>345</v>
       </c>
       <c r="B338" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
@@ -5140,7 +5131,7 @@
         <v>346</v>
       </c>
       <c r="B339" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -5148,7 +5139,7 @@
         <v>347</v>
       </c>
       <c r="B340" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
@@ -5156,7 +5147,7 @@
         <v>348</v>
       </c>
       <c r="B341" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
@@ -5164,7 +5155,7 @@
         <v>349</v>
       </c>
       <c r="B342" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
@@ -5172,31 +5163,31 @@
         <v>350</v>
       </c>
       <c r="B343" t="s">
-        <v>274</v>
+        <v>351</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B344" t="s">
-        <v>274</v>
+        <v>351</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B345" t="s">
-        <v>274</v>
+        <v>351</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B346" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
@@ -5204,7 +5195,7 @@
         <v>355</v>
       </c>
       <c r="B347" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
@@ -5212,7 +5203,7 @@
         <v>356</v>
       </c>
       <c r="B348" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
@@ -5220,7 +5211,7 @@
         <v>357</v>
       </c>
       <c r="B349" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
@@ -5228,7 +5219,7 @@
         <v>358</v>
       </c>
       <c r="B350" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -5236,7 +5227,7 @@
         <v>359</v>
       </c>
       <c r="B351" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -5244,7 +5235,7 @@
         <v>360</v>
       </c>
       <c r="B352" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
@@ -5252,7 +5243,7 @@
         <v>361</v>
       </c>
       <c r="B353" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
@@ -5260,7 +5251,7 @@
         <v>362</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
@@ -5268,7 +5259,7 @@
         <v>363</v>
       </c>
       <c r="B355" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
@@ -5276,7 +5267,7 @@
         <v>364</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -5284,7 +5275,7 @@
         <v>365</v>
       </c>
       <c r="B357" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
@@ -5292,7 +5283,7 @@
         <v>366</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -5300,7 +5291,7 @@
         <v>367</v>
       </c>
       <c r="B359" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -5308,7 +5299,7 @@
         <v>368</v>
       </c>
       <c r="B360" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
@@ -5316,7 +5307,7 @@
         <v>369</v>
       </c>
       <c r="B361" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
@@ -5324,7 +5315,7 @@
         <v>370</v>
       </c>
       <c r="B362" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
@@ -5332,7 +5323,7 @@
         <v>371</v>
       </c>
       <c r="B363" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
@@ -5340,7 +5331,7 @@
         <v>372</v>
       </c>
       <c r="B364" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
@@ -5348,7 +5339,7 @@
         <v>373</v>
       </c>
       <c r="B365" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
@@ -5356,7 +5347,7 @@
         <v>374</v>
       </c>
       <c r="B366" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
@@ -5364,7 +5355,7 @@
         <v>375</v>
       </c>
       <c r="B367" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
@@ -5372,7 +5363,7 @@
         <v>376</v>
       </c>
       <c r="B368" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
@@ -5380,7 +5371,7 @@
         <v>377</v>
       </c>
       <c r="B369" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
@@ -5388,7 +5379,7 @@
         <v>378</v>
       </c>
       <c r="B370" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
@@ -5396,7 +5387,7 @@
         <v>379</v>
       </c>
       <c r="B371" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -5404,7 +5395,7 @@
         <v>380</v>
       </c>
       <c r="B372" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
@@ -5412,7 +5403,7 @@
         <v>381</v>
       </c>
       <c r="B373" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -5420,7 +5411,7 @@
         <v>382</v>
       </c>
       <c r="B374" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
@@ -5428,7 +5419,7 @@
         <v>383</v>
       </c>
       <c r="B375" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -5436,7 +5427,7 @@
         <v>384</v>
       </c>
       <c r="B376" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
@@ -5444,7 +5435,7 @@
         <v>385</v>
       </c>
       <c r="B377" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -5452,7 +5443,7 @@
         <v>386</v>
       </c>
       <c r="B378" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
@@ -5460,7 +5451,7 @@
         <v>387</v>
       </c>
       <c r="B379" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -5468,7 +5459,7 @@
         <v>388</v>
       </c>
       <c r="B380" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
@@ -5476,7 +5467,7 @@
         <v>389</v>
       </c>
       <c r="B381" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
@@ -5484,7 +5475,7 @@
         <v>390</v>
       </c>
       <c r="B382" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
@@ -5492,7 +5483,7 @@
         <v>391</v>
       </c>
       <c r="B383" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
@@ -5500,7 +5491,7 @@
         <v>392</v>
       </c>
       <c r="B384" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
@@ -5508,7 +5499,7 @@
         <v>393</v>
       </c>
       <c r="B385" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
@@ -5516,7 +5507,7 @@
         <v>394</v>
       </c>
       <c r="B386" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
@@ -5524,7 +5515,7 @@
         <v>395</v>
       </c>
       <c r="B387" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
@@ -5532,7 +5523,7 @@
         <v>396</v>
       </c>
       <c r="B388" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
@@ -5540,7 +5531,7 @@
         <v>397</v>
       </c>
       <c r="B389" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -5548,7 +5539,7 @@
         <v>398</v>
       </c>
       <c r="B390" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
@@ -5556,7 +5547,7 @@
         <v>399</v>
       </c>
       <c r="B391" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
@@ -5564,7 +5555,7 @@
         <v>400</v>
       </c>
       <c r="B392" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
@@ -5572,7 +5563,7 @@
         <v>401</v>
       </c>
       <c r="B393" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
@@ -5580,7 +5571,7 @@
         <v>402</v>
       </c>
       <c r="B394" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
@@ -5588,7 +5579,7 @@
         <v>403</v>
       </c>
       <c r="B395" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
@@ -5596,7 +5587,7 @@
         <v>404</v>
       </c>
       <c r="B396" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -5604,7 +5595,7 @@
         <v>405</v>
       </c>
       <c r="B397" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
@@ -5612,7 +5603,7 @@
         <v>406</v>
       </c>
       <c r="B398" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
@@ -5620,7 +5611,7 @@
         <v>407</v>
       </c>
       <c r="B399" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
@@ -5628,7 +5619,7 @@
         <v>408</v>
       </c>
       <c r="B400" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
@@ -5636,7 +5627,7 @@
         <v>409</v>
       </c>
       <c r="B401" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
@@ -5644,7 +5635,7 @@
         <v>410</v>
       </c>
       <c r="B402" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -5652,7 +5643,7 @@
         <v>411</v>
       </c>
       <c r="B403" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -5660,7 +5651,7 @@
         <v>412</v>
       </c>
       <c r="B404" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
@@ -5668,7 +5659,7 @@
         <v>413</v>
       </c>
       <c r="B405" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
@@ -5676,7 +5667,7 @@
         <v>414</v>
       </c>
       <c r="B406" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
@@ -5684,7 +5675,7 @@
         <v>415</v>
       </c>
       <c r="B407" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
@@ -5692,7 +5683,7 @@
         <v>416</v>
       </c>
       <c r="B408" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -5700,7 +5691,7 @@
         <v>417</v>
       </c>
       <c r="B409" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
@@ -5708,7 +5699,7 @@
         <v>418</v>
       </c>
       <c r="B410" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -5716,7 +5707,7 @@
         <v>419</v>
       </c>
       <c r="B411" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
@@ -5724,7 +5715,7 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
@@ -5732,7 +5723,7 @@
         <v>421</v>
       </c>
       <c r="B413" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
@@ -5740,31 +5731,31 @@
         <v>422</v>
       </c>
       <c r="B414" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
+        <v>424</v>
+      </c>
+      <c r="B415" t="s">
         <v>423</v>
-      </c>
-      <c r="B415" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B416" t="s">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B417" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
@@ -5772,7 +5763,7 @@
         <v>427</v>
       </c>
       <c r="B418" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
@@ -5780,7 +5771,7 @@
         <v>428</v>
       </c>
       <c r="B419" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
@@ -5788,7 +5779,7 @@
         <v>429</v>
       </c>
       <c r="B420" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
@@ -5796,7 +5787,7 @@
         <v>430</v>
       </c>
       <c r="B421" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
@@ -5804,7 +5795,7 @@
         <v>431</v>
       </c>
       <c r="B422" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
@@ -5812,7 +5803,7 @@
         <v>432</v>
       </c>
       <c r="B423" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
@@ -5820,7 +5811,7 @@
         <v>433</v>
       </c>
       <c r="B424" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
@@ -5828,7 +5819,7 @@
         <v>434</v>
       </c>
       <c r="B425" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
@@ -5836,7 +5827,7 @@
         <v>435</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
@@ -5844,7 +5835,7 @@
         <v>436</v>
       </c>
       <c r="B427" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
@@ -5852,7 +5843,7 @@
         <v>437</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
@@ -5860,7 +5851,7 @@
         <v>438</v>
       </c>
       <c r="B429" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
@@ -5868,7 +5859,7 @@
         <v>439</v>
       </c>
       <c r="B430" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
@@ -5876,7 +5867,7 @@
         <v>440</v>
       </c>
       <c r="B431" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
@@ -5884,7 +5875,7 @@
         <v>441</v>
       </c>
       <c r="B432" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
@@ -5892,7 +5883,7 @@
         <v>442</v>
       </c>
       <c r="B433" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
@@ -5900,7 +5891,7 @@
         <v>443</v>
       </c>
       <c r="B434" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
@@ -5908,7 +5899,7 @@
         <v>444</v>
       </c>
       <c r="B435" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
@@ -5916,7 +5907,7 @@
         <v>445</v>
       </c>
       <c r="B436" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
@@ -5924,7 +5915,7 @@
         <v>446</v>
       </c>
       <c r="B437" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -5932,7 +5923,7 @@
         <v>447</v>
       </c>
       <c r="B438" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
@@ -5940,7 +5931,7 @@
         <v>448</v>
       </c>
       <c r="B439" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
@@ -5948,31 +5939,31 @@
         <v>449</v>
       </c>
       <c r="B440" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
+        <v>451</v>
+      </c>
+      <c r="B441" t="s">
         <v>450</v>
-      </c>
-      <c r="B441" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
@@ -5980,7 +5971,7 @@
         <v>454</v>
       </c>
       <c r="B444" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
@@ -5988,7 +5979,7 @@
         <v>455</v>
       </c>
       <c r="B445" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
@@ -5996,7 +5987,7 @@
         <v>456</v>
       </c>
       <c r="B446" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
@@ -6004,7 +5995,7 @@
         <v>457</v>
       </c>
       <c r="B447" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
@@ -6012,7 +6003,7 @@
         <v>458</v>
       </c>
       <c r="B448" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
@@ -6020,7 +6011,7 @@
         <v>459</v>
       </c>
       <c r="B449" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
@@ -6028,7 +6019,7 @@
         <v>460</v>
       </c>
       <c r="B450" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
@@ -6036,7 +6027,7 @@
         <v>461</v>
       </c>
       <c r="B451" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
@@ -6044,7 +6035,7 @@
         <v>462</v>
       </c>
       <c r="B452" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
@@ -6052,7 +6043,7 @@
         <v>463</v>
       </c>
       <c r="B453" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
@@ -6060,7 +6051,7 @@
         <v>464</v>
       </c>
       <c r="B454" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
@@ -6068,7 +6059,7 @@
         <v>465</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
@@ -6076,7 +6067,7 @@
         <v>466</v>
       </c>
       <c r="B456" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
@@ -6084,7 +6075,7 @@
         <v>467</v>
       </c>
       <c r="B457" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
@@ -6092,7 +6083,7 @@
         <v>468</v>
       </c>
       <c r="B458" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
@@ -6100,7 +6091,7 @@
         <v>469</v>
       </c>
       <c r="B459" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -6108,7 +6099,7 @@
         <v>470</v>
       </c>
       <c r="B460" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
@@ -6116,7 +6107,7 @@
         <v>471</v>
       </c>
       <c r="B461" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
@@ -6124,7 +6115,7 @@
         <v>472</v>
       </c>
       <c r="B462" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
@@ -6132,7 +6123,7 @@
         <v>473</v>
       </c>
       <c r="B463" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
@@ -6140,7 +6131,7 @@
         <v>474</v>
       </c>
       <c r="B464" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
@@ -6148,7 +6139,7 @@
         <v>475</v>
       </c>
       <c r="B465" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
@@ -6156,7 +6147,7 @@
         <v>476</v>
       </c>
       <c r="B466" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
@@ -6164,7 +6155,7 @@
         <v>477</v>
       </c>
       <c r="B467" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
@@ -6172,7 +6163,7 @@
         <v>478</v>
       </c>
       <c r="B468" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
@@ -6180,7 +6171,7 @@
         <v>479</v>
       </c>
       <c r="B469" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
@@ -6188,7 +6179,7 @@
         <v>480</v>
       </c>
       <c r="B470" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
@@ -6196,31 +6187,31 @@
         <v>481</v>
       </c>
       <c r="B471" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
+        <v>483</v>
+      </c>
+      <c r="B472" t="s">
         <v>482</v>
-      </c>
-      <c r="B472" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>453</v>
+        <v>482</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
@@ -6228,7 +6219,7 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
@@ -6236,7 +6227,7 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
@@ -6244,7 +6235,7 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -6252,7 +6243,7 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
@@ -6260,7 +6251,7 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
@@ -6268,7 +6259,7 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
@@ -6276,7 +6267,7 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
@@ -6284,7 +6275,7 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
@@ -6292,7 +6283,7 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
@@ -6300,7 +6291,7 @@
         <v>495</v>
       </c>
       <c r="B484" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
@@ -6308,7 +6299,7 @@
         <v>496</v>
       </c>
       <c r="B485" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
@@ -6316,7 +6307,7 @@
         <v>497</v>
       </c>
       <c r="B486" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
@@ -6324,7 +6315,7 @@
         <v>498</v>
       </c>
       <c r="B487" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
@@ -6332,7 +6323,7 @@
         <v>499</v>
       </c>
       <c r="B488" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
@@ -6340,7 +6331,7 @@
         <v>500</v>
       </c>
       <c r="B489" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
@@ -6348,7 +6339,7 @@
         <v>501</v>
       </c>
       <c r="B490" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
@@ -6356,7 +6347,7 @@
         <v>502</v>
       </c>
       <c r="B491" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
@@ -6364,7 +6355,7 @@
         <v>503</v>
       </c>
       <c r="B492" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
@@ -6372,7 +6363,7 @@
         <v>504</v>
       </c>
       <c r="B493" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -6380,7 +6371,7 @@
         <v>505</v>
       </c>
       <c r="B494" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
@@ -6388,7 +6379,7 @@
         <v>506</v>
       </c>
       <c r="B495" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
@@ -6396,7 +6387,7 @@
         <v>507</v>
       </c>
       <c r="B496" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -6404,7 +6395,7 @@
         <v>508</v>
       </c>
       <c r="B497" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
@@ -6412,7 +6403,7 @@
         <v>509</v>
       </c>
       <c r="B498" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
@@ -6420,7 +6411,7 @@
         <v>510</v>
       </c>
       <c r="B499" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
@@ -6428,7 +6419,7 @@
         <v>511</v>
       </c>
       <c r="B500" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
@@ -6436,31 +6427,7 @@
         <v>512</v>
       </c>
       <c r="B501" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A502" t="s">
-        <v>513</v>
-      </c>
-      <c r="B502" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A503" t="s">
-        <v>514</v>
-      </c>
-      <c r="B503" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A504" t="s">
-        <v>515</v>
-      </c>
-      <c r="B504" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/data/csv/SP500.xlsx
+++ b/data/csv/SP500.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfpin\Desktop\Projects\gravity\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38FE8A1-57E1-498A-B677-CCF8283B386F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF06B45A-DAA7-4B82-9187-611FBC9DF482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5CBD7DF0-9BE8-4B06-9E4B-6321E64942CB}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="512">
   <si>
     <t>Ticker</t>
   </si>
@@ -515,9 +515,6 @@
   </si>
   <si>
     <t>FIS</t>
-  </si>
-  <si>
-    <t>FISV</t>
   </si>
   <si>
     <t>FITB</t>
@@ -2419,7 +2416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEF72847-80E3-4E00-933E-448160A236EF}">
-  <dimension ref="A1:B501"/>
+  <dimension ref="A1:B500"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -4051,15 +4048,15 @@
         <v>209</v>
       </c>
       <c r="B204" t="s">
-        <v>135</v>
+        <v>210</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
+        <v>211</v>
+      </c>
+      <c r="B205" t="s">
         <v>210</v>
-      </c>
-      <c r="B205" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -4067,7 +4064,7 @@
         <v>212</v>
       </c>
       <c r="B206" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -4075,7 +4072,7 @@
         <v>213</v>
       </c>
       <c r="B207" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -4083,7 +4080,7 @@
         <v>214</v>
       </c>
       <c r="B208" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -4091,7 +4088,7 @@
         <v>215</v>
       </c>
       <c r="B209" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -4099,7 +4096,7 @@
         <v>216</v>
       </c>
       <c r="B210" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -4107,7 +4104,7 @@
         <v>217</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -4115,7 +4112,7 @@
         <v>218</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -4123,7 +4120,7 @@
         <v>219</v>
       </c>
       <c r="B213" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -4131,7 +4128,7 @@
         <v>220</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -4139,7 +4136,7 @@
         <v>221</v>
       </c>
       <c r="B215" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -4147,7 +4144,7 @@
         <v>222</v>
       </c>
       <c r="B216" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -4155,7 +4152,7 @@
         <v>223</v>
       </c>
       <c r="B217" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -4163,7 +4160,7 @@
         <v>224</v>
       </c>
       <c r="B218" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -4171,7 +4168,7 @@
         <v>225</v>
       </c>
       <c r="B219" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -4179,7 +4176,7 @@
         <v>226</v>
       </c>
       <c r="B220" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -4187,7 +4184,7 @@
         <v>227</v>
       </c>
       <c r="B221" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -4195,7 +4192,7 @@
         <v>228</v>
       </c>
       <c r="B222" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -4203,7 +4200,7 @@
         <v>229</v>
       </c>
       <c r="B223" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -4211,7 +4208,7 @@
         <v>230</v>
       </c>
       <c r="B224" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -4219,7 +4216,7 @@
         <v>231</v>
       </c>
       <c r="B225" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -4227,7 +4224,7 @@
         <v>232</v>
       </c>
       <c r="B226" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -4235,7 +4232,7 @@
         <v>233</v>
       </c>
       <c r="B227" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -4243,7 +4240,7 @@
         <v>234</v>
       </c>
       <c r="B228" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -4251,7 +4248,7 @@
         <v>235</v>
       </c>
       <c r="B229" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -4259,7 +4256,7 @@
         <v>236</v>
       </c>
       <c r="B230" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -4267,7 +4264,7 @@
         <v>237</v>
       </c>
       <c r="B231" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -4275,7 +4272,7 @@
         <v>238</v>
       </c>
       <c r="B232" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -4283,7 +4280,7 @@
         <v>239</v>
       </c>
       <c r="B233" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -4291,7 +4288,7 @@
         <v>240</v>
       </c>
       <c r="B234" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -4299,7 +4296,7 @@
         <v>241</v>
       </c>
       <c r="B235" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -4307,7 +4304,7 @@
         <v>242</v>
       </c>
       <c r="B236" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -4315,7 +4312,7 @@
         <v>243</v>
       </c>
       <c r="B237" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -4323,7 +4320,7 @@
         <v>244</v>
       </c>
       <c r="B238" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -4331,7 +4328,7 @@
         <v>245</v>
       </c>
       <c r="B239" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -4339,7 +4336,7 @@
         <v>246</v>
       </c>
       <c r="B240" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -4347,7 +4344,7 @@
         <v>247</v>
       </c>
       <c r="B241" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -4355,7 +4352,7 @@
         <v>248</v>
       </c>
       <c r="B242" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -4363,7 +4360,7 @@
         <v>249</v>
       </c>
       <c r="B243" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -4371,7 +4368,7 @@
         <v>250</v>
       </c>
       <c r="B244" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -4379,7 +4376,7 @@
         <v>251</v>
       </c>
       <c r="B245" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -4387,7 +4384,7 @@
         <v>252</v>
       </c>
       <c r="B246" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -4395,7 +4392,7 @@
         <v>253</v>
       </c>
       <c r="B247" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -4403,7 +4400,7 @@
         <v>254</v>
       </c>
       <c r="B248" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -4411,7 +4408,7 @@
         <v>255</v>
       </c>
       <c r="B249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -4419,7 +4416,7 @@
         <v>256</v>
       </c>
       <c r="B250" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -4427,7 +4424,7 @@
         <v>257</v>
       </c>
       <c r="B251" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -4435,7 +4432,7 @@
         <v>258</v>
       </c>
       <c r="B252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -4443,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="B253" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -4451,7 +4448,7 @@
         <v>260</v>
       </c>
       <c r="B254" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -4459,7 +4456,7 @@
         <v>261</v>
       </c>
       <c r="B255" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -4467,7 +4464,7 @@
         <v>262</v>
       </c>
       <c r="B256" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -4475,7 +4472,7 @@
         <v>263</v>
       </c>
       <c r="B257" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -4483,7 +4480,7 @@
         <v>264</v>
       </c>
       <c r="B258" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -4491,7 +4488,7 @@
         <v>265</v>
       </c>
       <c r="B259" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -4499,7 +4496,7 @@
         <v>266</v>
       </c>
       <c r="B260" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -4507,7 +4504,7 @@
         <v>267</v>
       </c>
       <c r="B261" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -4515,7 +4512,7 @@
         <v>268</v>
       </c>
       <c r="B262" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -4523,15 +4520,15 @@
         <v>269</v>
       </c>
       <c r="B263" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B264" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -4539,7 +4536,7 @@
         <v>272</v>
       </c>
       <c r="B265" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -4547,7 +4544,7 @@
         <v>273</v>
       </c>
       <c r="B266" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -4555,7 +4552,7 @@
         <v>274</v>
       </c>
       <c r="B267" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -4563,7 +4560,7 @@
         <v>275</v>
       </c>
       <c r="B268" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -4571,7 +4568,7 @@
         <v>276</v>
       </c>
       <c r="B269" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -4579,7 +4576,7 @@
         <v>277</v>
       </c>
       <c r="B270" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -4587,7 +4584,7 @@
         <v>278</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -4595,7 +4592,7 @@
         <v>279</v>
       </c>
       <c r="B272" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -4603,7 +4600,7 @@
         <v>280</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -4611,7 +4608,7 @@
         <v>281</v>
       </c>
       <c r="B274" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -4619,7 +4616,7 @@
         <v>282</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -4627,7 +4624,7 @@
         <v>283</v>
       </c>
       <c r="B276" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -4635,7 +4632,7 @@
         <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -4643,7 +4640,7 @@
         <v>285</v>
       </c>
       <c r="B278" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -4651,7 +4648,7 @@
         <v>286</v>
       </c>
       <c r="B279" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -4659,7 +4656,7 @@
         <v>287</v>
       </c>
       <c r="B280" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -4667,7 +4664,7 @@
         <v>288</v>
       </c>
       <c r="B281" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -4675,7 +4672,7 @@
         <v>289</v>
       </c>
       <c r="B282" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -4683,7 +4680,7 @@
         <v>290</v>
       </c>
       <c r="B283" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -4691,7 +4688,7 @@
         <v>291</v>
       </c>
       <c r="B284" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -4699,7 +4696,7 @@
         <v>292</v>
       </c>
       <c r="B285" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -4707,7 +4704,7 @@
         <v>293</v>
       </c>
       <c r="B286" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -4715,7 +4712,7 @@
         <v>294</v>
       </c>
       <c r="B287" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -4723,7 +4720,7 @@
         <v>295</v>
       </c>
       <c r="B288" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -4731,7 +4728,7 @@
         <v>296</v>
       </c>
       <c r="B289" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -4739,7 +4736,7 @@
         <v>297</v>
       </c>
       <c r="B290" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -4747,7 +4744,7 @@
         <v>298</v>
       </c>
       <c r="B291" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -4755,7 +4752,7 @@
         <v>299</v>
       </c>
       <c r="B292" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -4763,7 +4760,7 @@
         <v>300</v>
       </c>
       <c r="B293" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -4771,7 +4768,7 @@
         <v>301</v>
       </c>
       <c r="B294" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -4779,7 +4776,7 @@
         <v>302</v>
       </c>
       <c r="B295" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -4787,7 +4784,7 @@
         <v>303</v>
       </c>
       <c r="B296" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -4795,7 +4792,7 @@
         <v>304</v>
       </c>
       <c r="B297" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -4803,7 +4800,7 @@
         <v>305</v>
       </c>
       <c r="B298" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -4811,7 +4808,7 @@
         <v>306</v>
       </c>
       <c r="B299" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -4819,7 +4816,7 @@
         <v>307</v>
       </c>
       <c r="B300" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -4827,7 +4824,7 @@
         <v>308</v>
       </c>
       <c r="B301" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -4835,7 +4832,7 @@
         <v>309</v>
       </c>
       <c r="B302" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
@@ -4843,7 +4840,7 @@
         <v>310</v>
       </c>
       <c r="B303" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
@@ -4851,7 +4848,7 @@
         <v>311</v>
       </c>
       <c r="B304" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
@@ -4859,7 +4856,7 @@
         <v>312</v>
       </c>
       <c r="B305" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
@@ -4867,7 +4864,7 @@
         <v>313</v>
       </c>
       <c r="B306" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
@@ -4875,7 +4872,7 @@
         <v>314</v>
       </c>
       <c r="B307" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
@@ -4883,7 +4880,7 @@
         <v>315</v>
       </c>
       <c r="B308" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
@@ -4891,7 +4888,7 @@
         <v>316</v>
       </c>
       <c r="B309" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
@@ -4899,7 +4896,7 @@
         <v>317</v>
       </c>
       <c r="B310" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -4907,7 +4904,7 @@
         <v>318</v>
       </c>
       <c r="B311" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
@@ -4915,7 +4912,7 @@
         <v>319</v>
       </c>
       <c r="B312" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
@@ -4923,7 +4920,7 @@
         <v>320</v>
       </c>
       <c r="B313" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
@@ -4931,7 +4928,7 @@
         <v>321</v>
       </c>
       <c r="B314" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
@@ -4939,7 +4936,7 @@
         <v>322</v>
       </c>
       <c r="B315" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -4947,7 +4944,7 @@
         <v>323</v>
       </c>
       <c r="B316" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
@@ -4955,7 +4952,7 @@
         <v>324</v>
       </c>
       <c r="B317" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
@@ -4963,7 +4960,7 @@
         <v>325</v>
       </c>
       <c r="B318" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
@@ -4971,7 +4968,7 @@
         <v>326</v>
       </c>
       <c r="B319" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
@@ -4979,7 +4976,7 @@
         <v>327</v>
       </c>
       <c r="B320" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
@@ -4987,7 +4984,7 @@
         <v>328</v>
       </c>
       <c r="B321" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
@@ -4995,7 +4992,7 @@
         <v>329</v>
       </c>
       <c r="B322" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -5003,7 +5000,7 @@
         <v>330</v>
       </c>
       <c r="B323" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
@@ -5011,7 +5008,7 @@
         <v>331</v>
       </c>
       <c r="B324" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -5019,7 +5016,7 @@
         <v>332</v>
       </c>
       <c r="B325" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
@@ -5027,7 +5024,7 @@
         <v>333</v>
       </c>
       <c r="B326" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -5035,7 +5032,7 @@
         <v>334</v>
       </c>
       <c r="B327" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
@@ -5043,7 +5040,7 @@
         <v>335</v>
       </c>
       <c r="B328" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -5051,7 +5048,7 @@
         <v>336</v>
       </c>
       <c r="B329" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
@@ -5059,7 +5056,7 @@
         <v>337</v>
       </c>
       <c r="B330" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -5067,7 +5064,7 @@
         <v>338</v>
       </c>
       <c r="B331" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
@@ -5075,7 +5072,7 @@
         <v>339</v>
       </c>
       <c r="B332" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -5083,7 +5080,7 @@
         <v>340</v>
       </c>
       <c r="B333" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
@@ -5091,7 +5088,7 @@
         <v>341</v>
       </c>
       <c r="B334" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
@@ -5099,7 +5096,7 @@
         <v>342</v>
       </c>
       <c r="B335" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
@@ -5107,7 +5104,7 @@
         <v>343</v>
       </c>
       <c r="B336" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
@@ -5115,7 +5112,7 @@
         <v>344</v>
       </c>
       <c r="B337" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
@@ -5123,7 +5120,7 @@
         <v>345</v>
       </c>
       <c r="B338" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
@@ -5131,7 +5128,7 @@
         <v>346</v>
       </c>
       <c r="B339" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -5139,7 +5136,7 @@
         <v>347</v>
       </c>
       <c r="B340" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
@@ -5147,7 +5144,7 @@
         <v>348</v>
       </c>
       <c r="B341" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
@@ -5155,15 +5152,15 @@
         <v>349</v>
       </c>
       <c r="B342" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B343" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
@@ -5171,7 +5168,7 @@
         <v>352</v>
       </c>
       <c r="B344" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
@@ -5179,7 +5176,7 @@
         <v>353</v>
       </c>
       <c r="B345" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
@@ -5187,7 +5184,7 @@
         <v>354</v>
       </c>
       <c r="B346" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
@@ -5195,7 +5192,7 @@
         <v>355</v>
       </c>
       <c r="B347" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
@@ -5203,7 +5200,7 @@
         <v>356</v>
       </c>
       <c r="B348" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
@@ -5211,7 +5208,7 @@
         <v>357</v>
       </c>
       <c r="B349" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
@@ -5219,7 +5216,7 @@
         <v>358</v>
       </c>
       <c r="B350" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
@@ -5227,7 +5224,7 @@
         <v>359</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
@@ -5235,7 +5232,7 @@
         <v>360</v>
       </c>
       <c r="B352" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
@@ -5243,7 +5240,7 @@
         <v>361</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
@@ -5251,7 +5248,7 @@
         <v>362</v>
       </c>
       <c r="B354" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
@@ -5259,7 +5256,7 @@
         <v>363</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
@@ -5267,7 +5264,7 @@
         <v>364</v>
       </c>
       <c r="B356" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
@@ -5275,7 +5272,7 @@
         <v>365</v>
       </c>
       <c r="B357" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
@@ -5283,7 +5280,7 @@
         <v>366</v>
       </c>
       <c r="B358" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
@@ -5291,7 +5288,7 @@
         <v>367</v>
       </c>
       <c r="B359" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
@@ -5299,7 +5296,7 @@
         <v>368</v>
       </c>
       <c r="B360" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
@@ -5307,7 +5304,7 @@
         <v>369</v>
       </c>
       <c r="B361" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
@@ -5315,7 +5312,7 @@
         <v>370</v>
       </c>
       <c r="B362" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
@@ -5323,7 +5320,7 @@
         <v>371</v>
       </c>
       <c r="B363" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
@@ -5331,7 +5328,7 @@
         <v>372</v>
       </c>
       <c r="B364" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
@@ -5339,7 +5336,7 @@
         <v>373</v>
       </c>
       <c r="B365" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
@@ -5347,7 +5344,7 @@
         <v>374</v>
       </c>
       <c r="B366" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
@@ -5355,7 +5352,7 @@
         <v>375</v>
       </c>
       <c r="B367" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
@@ -5363,7 +5360,7 @@
         <v>376</v>
       </c>
       <c r="B368" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
@@ -5371,7 +5368,7 @@
         <v>377</v>
       </c>
       <c r="B369" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
@@ -5379,7 +5376,7 @@
         <v>378</v>
       </c>
       <c r="B370" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
@@ -5387,7 +5384,7 @@
         <v>379</v>
       </c>
       <c r="B371" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
@@ -5395,7 +5392,7 @@
         <v>380</v>
       </c>
       <c r="B372" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
@@ -5403,7 +5400,7 @@
         <v>381</v>
       </c>
       <c r="B373" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
@@ -5411,7 +5408,7 @@
         <v>382</v>
       </c>
       <c r="B374" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
@@ -5419,7 +5416,7 @@
         <v>383</v>
       </c>
       <c r="B375" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
@@ -5427,7 +5424,7 @@
         <v>384</v>
       </c>
       <c r="B376" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
@@ -5435,7 +5432,7 @@
         <v>385</v>
       </c>
       <c r="B377" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
@@ -5443,7 +5440,7 @@
         <v>386</v>
       </c>
       <c r="B378" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
@@ -5451,7 +5448,7 @@
         <v>387</v>
       </c>
       <c r="B379" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
@@ -5459,7 +5456,7 @@
         <v>388</v>
       </c>
       <c r="B380" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
@@ -5467,7 +5464,7 @@
         <v>389</v>
       </c>
       <c r="B381" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
@@ -5475,7 +5472,7 @@
         <v>390</v>
       </c>
       <c r="B382" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
@@ -5483,7 +5480,7 @@
         <v>391</v>
       </c>
       <c r="B383" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
@@ -5491,7 +5488,7 @@
         <v>392</v>
       </c>
       <c r="B384" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
@@ -5499,7 +5496,7 @@
         <v>393</v>
       </c>
       <c r="B385" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
@@ -5507,7 +5504,7 @@
         <v>394</v>
       </c>
       <c r="B386" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
@@ -5515,7 +5512,7 @@
         <v>395</v>
       </c>
       <c r="B387" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
@@ -5523,7 +5520,7 @@
         <v>396</v>
       </c>
       <c r="B388" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
@@ -5531,7 +5528,7 @@
         <v>397</v>
       </c>
       <c r="B389" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
@@ -5539,7 +5536,7 @@
         <v>398</v>
       </c>
       <c r="B390" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
@@ -5547,7 +5544,7 @@
         <v>399</v>
       </c>
       <c r="B391" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
@@ -5555,7 +5552,7 @@
         <v>400</v>
       </c>
       <c r="B392" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
@@ -5563,7 +5560,7 @@
         <v>401</v>
       </c>
       <c r="B393" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
@@ -5571,7 +5568,7 @@
         <v>402</v>
       </c>
       <c r="B394" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
@@ -5579,7 +5576,7 @@
         <v>403</v>
       </c>
       <c r="B395" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
@@ -5587,7 +5584,7 @@
         <v>404</v>
       </c>
       <c r="B396" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
@@ -5595,7 +5592,7 @@
         <v>405</v>
       </c>
       <c r="B397" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
@@ -5603,7 +5600,7 @@
         <v>406</v>
       </c>
       <c r="B398" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
@@ -5611,7 +5608,7 @@
         <v>407</v>
       </c>
       <c r="B399" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
@@ -5619,7 +5616,7 @@
         <v>408</v>
       </c>
       <c r="B400" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
@@ -5627,7 +5624,7 @@
         <v>409</v>
       </c>
       <c r="B401" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
@@ -5635,7 +5632,7 @@
         <v>410</v>
       </c>
       <c r="B402" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -5643,7 +5640,7 @@
         <v>411</v>
       </c>
       <c r="B403" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
@@ -5651,7 +5648,7 @@
         <v>412</v>
       </c>
       <c r="B404" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
@@ -5659,7 +5656,7 @@
         <v>413</v>
       </c>
       <c r="B405" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
@@ -5667,7 +5664,7 @@
         <v>414</v>
       </c>
       <c r="B406" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
@@ -5675,7 +5672,7 @@
         <v>415</v>
       </c>
       <c r="B407" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
@@ -5683,7 +5680,7 @@
         <v>416</v>
       </c>
       <c r="B408" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
@@ -5691,7 +5688,7 @@
         <v>417</v>
       </c>
       <c r="B409" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
@@ -5699,7 +5696,7 @@
         <v>418</v>
       </c>
       <c r="B410" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
@@ -5707,7 +5704,7 @@
         <v>419</v>
       </c>
       <c r="B411" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
@@ -5715,7 +5712,7 @@
         <v>420</v>
       </c>
       <c r="B412" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
@@ -5723,15 +5720,15 @@
         <v>421</v>
       </c>
       <c r="B413" t="s">
-        <v>351</v>
+        <v>422</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
+        <v>423</v>
+      </c>
+      <c r="B414" t="s">
         <v>422</v>
-      </c>
-      <c r="B414" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
@@ -5739,7 +5736,7 @@
         <v>424</v>
       </c>
       <c r="B415" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
@@ -5747,7 +5744,7 @@
         <v>425</v>
       </c>
       <c r="B416" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
@@ -5755,7 +5752,7 @@
         <v>426</v>
       </c>
       <c r="B417" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
@@ -5763,7 +5760,7 @@
         <v>427</v>
       </c>
       <c r="B418" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
@@ -5771,7 +5768,7 @@
         <v>428</v>
       </c>
       <c r="B419" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
@@ -5779,7 +5776,7 @@
         <v>429</v>
       </c>
       <c r="B420" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
@@ -5787,7 +5784,7 @@
         <v>430</v>
       </c>
       <c r="B421" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
@@ -5795,7 +5792,7 @@
         <v>431</v>
       </c>
       <c r="B422" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
@@ -5803,7 +5800,7 @@
         <v>432</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
@@ -5811,7 +5808,7 @@
         <v>433</v>
       </c>
       <c r="B424" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
@@ -5819,7 +5816,7 @@
         <v>434</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
@@ -5827,7 +5824,7 @@
         <v>435</v>
       </c>
       <c r="B426" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
@@ -5835,7 +5832,7 @@
         <v>436</v>
       </c>
       <c r="B427" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
@@ -5843,7 +5840,7 @@
         <v>437</v>
       </c>
       <c r="B428" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
@@ -5851,7 +5848,7 @@
         <v>438</v>
       </c>
       <c r="B429" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
@@ -5859,7 +5856,7 @@
         <v>439</v>
       </c>
       <c r="B430" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
@@ -5867,7 +5864,7 @@
         <v>440</v>
       </c>
       <c r="B431" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
@@ -5875,7 +5872,7 @@
         <v>441</v>
       </c>
       <c r="B432" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
@@ -5883,7 +5880,7 @@
         <v>442</v>
       </c>
       <c r="B433" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
@@ -5891,7 +5888,7 @@
         <v>443</v>
       </c>
       <c r="B434" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
@@ -5899,7 +5896,7 @@
         <v>444</v>
       </c>
       <c r="B435" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
@@ -5907,7 +5904,7 @@
         <v>445</v>
       </c>
       <c r="B436" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
@@ -5915,7 +5912,7 @@
         <v>446</v>
       </c>
       <c r="B437" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
@@ -5923,7 +5920,7 @@
         <v>447</v>
       </c>
       <c r="B438" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
@@ -5931,15 +5928,15 @@
         <v>448</v>
       </c>
       <c r="B439" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
+        <v>450</v>
+      </c>
+      <c r="B440" t="s">
         <v>449</v>
-      </c>
-      <c r="B440" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
@@ -5947,7 +5944,7 @@
         <v>451</v>
       </c>
       <c r="B441" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
@@ -5955,7 +5952,7 @@
         <v>452</v>
       </c>
       <c r="B442" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
@@ -5963,7 +5960,7 @@
         <v>453</v>
       </c>
       <c r="B443" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
@@ -5971,7 +5968,7 @@
         <v>454</v>
       </c>
       <c r="B444" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
@@ -5979,7 +5976,7 @@
         <v>455</v>
       </c>
       <c r="B445" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
@@ -5987,7 +5984,7 @@
         <v>456</v>
       </c>
       <c r="B446" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
@@ -5995,7 +5992,7 @@
         <v>457</v>
       </c>
       <c r="B447" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
@@ -6003,7 +6000,7 @@
         <v>458</v>
       </c>
       <c r="B448" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
@@ -6011,7 +6008,7 @@
         <v>459</v>
       </c>
       <c r="B449" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
@@ -6019,7 +6016,7 @@
         <v>460</v>
       </c>
       <c r="B450" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
@@ -6027,7 +6024,7 @@
         <v>461</v>
       </c>
       <c r="B451" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
@@ -6035,7 +6032,7 @@
         <v>462</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
@@ -6043,7 +6040,7 @@
         <v>463</v>
       </c>
       <c r="B453" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
@@ -6051,7 +6048,7 @@
         <v>464</v>
       </c>
       <c r="B454" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
@@ -6059,7 +6056,7 @@
         <v>465</v>
       </c>
       <c r="B455" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
@@ -6067,7 +6064,7 @@
         <v>466</v>
       </c>
       <c r="B456" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
@@ -6075,7 +6072,7 @@
         <v>467</v>
       </c>
       <c r="B457" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
@@ -6083,7 +6080,7 @@
         <v>468</v>
       </c>
       <c r="B458" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
@@ -6091,7 +6088,7 @@
         <v>469</v>
       </c>
       <c r="B459" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -6099,7 +6096,7 @@
         <v>470</v>
       </c>
       <c r="B460" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
@@ -6107,7 +6104,7 @@
         <v>471</v>
       </c>
       <c r="B461" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
@@ -6115,7 +6112,7 @@
         <v>472</v>
       </c>
       <c r="B462" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
@@ -6123,7 +6120,7 @@
         <v>473</v>
       </c>
       <c r="B463" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
@@ -6131,7 +6128,7 @@
         <v>474</v>
       </c>
       <c r="B464" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
@@ -6139,7 +6136,7 @@
         <v>475</v>
       </c>
       <c r="B465" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
@@ -6147,7 +6144,7 @@
         <v>476</v>
       </c>
       <c r="B466" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
@@ -6155,7 +6152,7 @@
         <v>477</v>
       </c>
       <c r="B467" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
@@ -6163,7 +6160,7 @@
         <v>478</v>
       </c>
       <c r="B468" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
@@ -6171,7 +6168,7 @@
         <v>479</v>
       </c>
       <c r="B469" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
@@ -6179,15 +6176,15 @@
         <v>480</v>
       </c>
       <c r="B470" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
+        <v>482</v>
+      </c>
+      <c r="B471" t="s">
         <v>481</v>
-      </c>
-      <c r="B471" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
@@ -6195,7 +6192,7 @@
         <v>483</v>
       </c>
       <c r="B472" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
@@ -6203,7 +6200,7 @@
         <v>484</v>
       </c>
       <c r="B473" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
@@ -6211,7 +6208,7 @@
         <v>485</v>
       </c>
       <c r="B474" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
@@ -6219,7 +6216,7 @@
         <v>486</v>
       </c>
       <c r="B475" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
@@ -6227,7 +6224,7 @@
         <v>487</v>
       </c>
       <c r="B476" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
@@ -6235,7 +6232,7 @@
         <v>488</v>
       </c>
       <c r="B477" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -6243,7 +6240,7 @@
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
@@ -6251,7 +6248,7 @@
         <v>490</v>
       </c>
       <c r="B479" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
@@ -6259,7 +6256,7 @@
         <v>491</v>
       </c>
       <c r="B480" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
@@ -6267,7 +6264,7 @@
         <v>492</v>
       </c>
       <c r="B481" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
@@ -6275,7 +6272,7 @@
         <v>493</v>
       </c>
       <c r="B482" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
@@ -6283,7 +6280,7 @@
         <v>494</v>
       </c>
       <c r="B483" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
@@ -6291,7 +6288,7 @@
         <v>495</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
@@ -6299,7 +6296,7 @@
         <v>496</v>
       </c>
       <c r="B485" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
@@ -6307,7 +6304,7 @@
         <v>497</v>
       </c>
       <c r="B486" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
@@ -6315,7 +6312,7 @@
         <v>498</v>
       </c>
       <c r="B487" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
@@ -6323,7 +6320,7 @@
         <v>499</v>
       </c>
       <c r="B488" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
@@ -6331,7 +6328,7 @@
         <v>500</v>
       </c>
       <c r="B489" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
@@ -6339,7 +6336,7 @@
         <v>501</v>
       </c>
       <c r="B490" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
@@ -6347,7 +6344,7 @@
         <v>502</v>
       </c>
       <c r="B491" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
@@ -6355,7 +6352,7 @@
         <v>503</v>
       </c>
       <c r="B492" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
@@ -6363,7 +6360,7 @@
         <v>504</v>
       </c>
       <c r="B493" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
@@ -6371,7 +6368,7 @@
         <v>505</v>
       </c>
       <c r="B494" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
@@ -6379,7 +6376,7 @@
         <v>506</v>
       </c>
       <c r="B495" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
@@ -6387,7 +6384,7 @@
         <v>507</v>
       </c>
       <c r="B496" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
@@ -6395,7 +6392,7 @@
         <v>508</v>
       </c>
       <c r="B497" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
@@ -6403,7 +6400,7 @@
         <v>509</v>
       </c>
       <c r="B498" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
@@ -6411,7 +6408,7 @@
         <v>510</v>
       </c>
       <c r="B499" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
@@ -6419,15 +6416,7 @@
         <v>511</v>
       </c>
       <c r="B500" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A501" t="s">
-        <v>512</v>
-      </c>
-      <c r="B501" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/data/csv/SP500.xlsx
+++ b/data/csv/SP500.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfpin\Desktop\Projects\gravity\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6A5977-6417-4B4D-88C6-D7FCBFFB25DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045AB824-30C6-4017-8CFC-58F122378B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5CBD7DF0-9BE8-4B06-9E4B-6321E64942CB}"/>
   </bookViews>
@@ -3237,9 +3237,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
